--- a/光伏配储项目/电价数据/2026/仰天站.xlsx
+++ b/光伏配储项目/电价数据/2026/仰天站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50763</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.76028</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56975</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5714400000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.50722</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51036</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43193</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.44781</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42289</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40404</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.3937</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3928</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4161</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40957</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.41934</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.43709</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.48434</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.25204</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.25181</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.00548</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.16245</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.25246</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.11322</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.11833</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.19463</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.19949</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.18389</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.18747</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.13485</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.44159</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5569500000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5224099999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7336</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.09617</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.03723</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43185</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43744</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6604</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.83839</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44711</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.17158</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.74949</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.55816</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.0409</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.25559</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41146</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65687</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7078099999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.18743</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.00806</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.88059</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79887</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7597699999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51762</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48188</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46886</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42667</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71401</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8802000000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.92924</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49876</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52081</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5067699999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50698</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48904</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47078</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38134</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37426</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38626</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.43055</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.03792</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.8873099999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.96329</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.47706</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.46662</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42087</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50636</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.24303</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.23565</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.17617</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.09272</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.5881000000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.7824</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.21116</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.78983</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.72011</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.18201</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.25888</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.60212</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.92399</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.04026</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.27326</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.4067</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.38466</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.47694</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.7349600000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.61719</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7609199999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.77601</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.15938</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.2455</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.16673</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8479</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20366</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.1047</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25682</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02975</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.08944</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.64697</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98238</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90862</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.96529</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8184</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.9250700000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.7620399999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.76041</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45142</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.75447</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.7795599999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42932</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3348</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51115</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49021</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44845</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41564</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38421</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43016</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39748</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36199</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39786</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47554</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44556</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44027</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39575</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.47221</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27711</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.09046</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.45569</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.02678</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.00903</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.20218</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.07371</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.60051</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.26075</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.53995</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.60756</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.49036</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7988099999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.55436</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.57492</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.44199</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.46065</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.00959</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39256</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.46051</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.46651</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.47068</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.54359</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.54314</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.47747</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.49998</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28029</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61963</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6243</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46414</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5063299999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.50256</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.58697</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.54026</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.62107</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.43487</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42418</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48447</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61499</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.61082</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5604199999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7424400000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6232300000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.53874</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.58348</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44133</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45798</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34218</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52266</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49712</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45088</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.4050299999999999</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.20821</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.17931</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.26855</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28485</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.18235</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.59977</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48563</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.43235</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.19236</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.24397</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6131799999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.46343</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28617</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.46401</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.48372</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.43951</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50284</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46495</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47509</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.50263</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.56251</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.4403</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55561</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.4802</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46175</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50136</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42347</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41874</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32107</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.40761</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.21714</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.14288</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.20015</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.16394</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14741</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.21594</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.01665</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.13978</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.13378</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.09268000000000001</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.11541</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.02683</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.008410000000000001</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2637</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.41221</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.42056</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.47471</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40909</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.51828</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35881</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.7326699999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.49387</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.46422</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.46928</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.45115</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10238</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04334</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01395</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21371</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19412</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04774</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06784999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06609000000000001</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33999</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31952</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.41474</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42849</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45691</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78538</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86288</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29621</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8875</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18708</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86849</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.52512</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33085</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03291</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5280499999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39989</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20699</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62185</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.42103</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.44195</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45237</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.41819</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.61727</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.46054</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.6080800000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.76567</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.88087</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46954</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.44805</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.6135900000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.46904</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.9405399999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.69412</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8665</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87499</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.46923</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.7755</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.7518899999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59674</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.43515</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.43834</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.48584</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.44118</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.36043</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9253400000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.48936</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.44819</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.42734</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.49845</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.43248</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.54323</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.40887</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.26449</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.13742</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19964</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25675</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.40308</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.47767</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.45914</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.44183</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.36668</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4249</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.6675599999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.9119700000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.47568</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.17607</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.71141</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80265</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66246</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.6653600000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.5063299999999999</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.46043</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.51105</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44965</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.46061</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.42179</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.44464</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.54415</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.42164</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.44328</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.44027</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.44316</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4609</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.48839</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.40485</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.43187</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.46771</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.42026</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.42635</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.45715</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.43017</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.50351</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5821799999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.40511</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25045</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15968</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28359</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27614</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.004940000000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26265</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25673</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29451</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.42139</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.6019</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.49535</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.9113600000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.49921</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.47058</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.48136</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.34127</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.45898</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.40326</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.4382200000000001</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.41079</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.44855</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22173</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.11255</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.12148</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27951</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.13144</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.11671</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.11847</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.25946</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.12341</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24001</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.11706</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25366</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28717</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.17197</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.09318000000000001</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.0722</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.09483</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.09673999999999999</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.18188</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.11256</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27967</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36894</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.48542</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.42611</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.48905</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.47611</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.47407</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.47966</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.41028</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.36557</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5955900000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39609</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.50834</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.45242</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.44301</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.41446</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37752</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.41248</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.48796</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26405</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.21106</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24954</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23167</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.09545999999999999</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.12877</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.1606</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30174</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24812</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.59815</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.38833</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.38784</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.45718</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.40363</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.37409</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.5560700000000001</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56587</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.3767799999999999</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.42187</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.18306</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6815399999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.47819</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46027</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.25851</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42574</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.23508</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24756</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.27162</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.14635</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.68736</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.16634</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.22716</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.25779</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3522</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.40296</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.42106</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.60799</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.46567</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.38834</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44903</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.43087</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7037</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.87738</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.76967</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.6348400000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.51755</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.25718</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.49264</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.37662</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.4646</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42574</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39376</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33277</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.40319</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.37097</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.40874</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.35306</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.39405</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.41342</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.41022</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.44224</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35724</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.45517</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.36722</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35745</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36901</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.45216</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.42156</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.66398</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.9013300000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.49431</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.44592</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.35564</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41989</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.38497</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.37333</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.36752</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.36526</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.36666</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.34315</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25913</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.11981</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29962</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.12825</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.12226</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.16509</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.11323</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.14673</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.14811</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.26749</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.18781</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.23763</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.27308</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.26444</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29643</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.29942</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.47919</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42991</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.65755</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.61539</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6219600000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5571900000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.82448</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.54173</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.97615</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.5280499999999999</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.50224</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4138</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.53038</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4636</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.44902</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.39555</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.37346</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.53334</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.64263</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.56526</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.78313</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.44334</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.44444</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.42553</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.43589</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.43187</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.44303</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.42016</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.40277</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.43147</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.42922</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.44884</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.44648</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.41271</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.43117</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.42674</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.44076</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.42876</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.49714</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.49121</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.6339</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.55374</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.48923</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.54715</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.48639</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47373</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40451</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.39655</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.48818</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.48535</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.56838</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.44254</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.43557</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29946</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40023</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6499400000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40749</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.85188</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.40688</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38986</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.39031</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.40481</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.40698</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.43812</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.46755</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.53822</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.48715</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5655399999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.56723</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.6187</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.80852</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.9843500000000001</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.0838</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7732599999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.93521</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.7897799999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.6095900000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.9685499999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7783099999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.68057</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.50632</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.5297000000000001</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.52819</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.5198700000000001</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.51223</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.44347</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.6141</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.45738</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47507</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.49375</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.44253</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43245</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.48147</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.42278</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.5071100000000001</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.43591</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.40751</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36824</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.48062</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.37401</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.41968</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40354</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40739</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.41515</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.27033</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40965</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.58624</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.19425</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.27047</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42972</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.49223</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.43989</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.05578</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.15378</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.1386</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.36114</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.41355</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4421</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.42552</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.48096</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.41615</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.43613</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.43223</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.43993</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.45699</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.44768</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.41208</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.43066</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.40281</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.43659</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.39717</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.41334</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.45255</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.43571</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.4090299999999999</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.55401</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.42749</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.44276</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43875</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.40091</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.48399</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.45949</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.40066</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.46312</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.4355</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.37997</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.42212</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.42909</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.28124</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.20872</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.23185</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.23151</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.20302</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24126</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27536</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.13472</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15503</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21147</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24274</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26706</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.22531</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28532</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.42685</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.41206</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.41753</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.43952</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.41378</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.40677</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.41297</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.42663</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.37811</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.3567</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.38874</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.28028</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.02381</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00015</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14863</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02137</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01503</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04288</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04077</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04859</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02925</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03773</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01681</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03594</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20302</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26588</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27999</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.39351</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.48054</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.36883</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.9614199999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.81609</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.4382</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.6594500000000001</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.45986</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.47809</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.5061600000000001</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.4068</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40417</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.46923</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38861</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.48646</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.41323</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.47052</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.43935</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.48167</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.44903</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.45115</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.46935</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.50297</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.43661</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.44432</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.10406</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.13065</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.89074</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8524700000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10221</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.1193</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.14588</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.10083</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.1285</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.11147</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.06591</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.02825</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.09045</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.0248</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.09997</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.00244</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.09473999999999999</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.12647</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25463</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.42767</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.40358</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.42165</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.92296</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.96463</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.94857</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.61573</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9913500000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.95816</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.9448099999999999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.97781</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8519099999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.85011</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.85439</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.95133</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.95601</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.97374</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.9544199999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.39423</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.53864</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.75742</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.07646</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.71062</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.50632</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.54623</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.46352</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45886</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.39395</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.43239</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.44771</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.58586</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.45902</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.4454</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.42826</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.43962</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5432400000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5778</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.43557</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.45757</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41017</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.40959</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.38128</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.36299</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.13945</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.14036</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.17614</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.2543</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.23154</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.27506</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26169</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.27725</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.4095299999999999</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.39625</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.54786</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.01064</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.46099</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.76954</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.54299</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.41656</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.49076</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.48201</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.58614</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.38424</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.38145</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.37467</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.46354</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.4747</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.45108</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.43933</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.42384</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.41371</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.37276</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38344</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.48638</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.40605</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.72333</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.8992</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.70497</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.65191</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.50346</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30041</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42429</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39619</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41063</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.7283999999999999</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8217300000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.44601</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5295599999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.54953</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.61212</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.82284</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5231399999999999</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.83589</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.6974400000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.54377</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.5450499999999999</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43217</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.42616</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.47674</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.48752</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.41888</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.26194</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.38085</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.49675</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.41609</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.41931</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.39267</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.39103</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.42163</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43496</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.38826</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.32072</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39253</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39418</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.39501</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43635</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.78564</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.87188</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.6890599999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.9563400000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.06157</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.7013200000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51351</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.8663200000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.70324</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.58021</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.29429</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.86742</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.68935</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.43406</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.31043</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.90885</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46893</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.41324</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.38506</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37943</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.38419</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.19538</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.28296</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.18399</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.24388</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.25932</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.06426999999999999</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.08493000000000001</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26843</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.09331999999999999</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.18874</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.1166</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.13359</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.12811</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.24122</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.19697</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.21804</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31568</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.41198</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.38338</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.40668</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5226799999999999</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42853</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.43688</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48579</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.4367799999999999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.41147</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40464</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41019</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.44807</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37214</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.39439</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.11599</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.41825</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.28848</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.7133200000000001</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.46157</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.8274</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.45227</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39553</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.27918</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.23588</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.25287</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.64381</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.24557</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.74007</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.25662</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.27226</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.25409</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.28099</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.2662</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.2799700000000001</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.40077</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.39789</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.45973</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.40884</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.40509</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42503</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41461</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37565</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.44785</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.41604</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.39127</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.37268</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.37298</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.37429</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17557</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29094</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14525</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19791</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.05146</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.27038</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.00014</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04558</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.15363</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.10021</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.12518</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07786</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.18071</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.1965</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.14384</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22681</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26517</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15632</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.05368999999999999</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.28747</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.15236</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19864</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14528</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.2563</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.39129</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37224</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.39626</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.40238</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.40265</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39293</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41507</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49104</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.40579</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.4034700000000001</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.40457</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3975</v>
       </c>
     </row>
   </sheetData>
